--- a/sim/resources/sample/BuildingAreaTable.xlsx
+++ b/sim/resources/sample/BuildingAreaTable.xlsx
@@ -80,12 +80,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+10-导玩员
+20-服务员
+30-管理员</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -114,6 +138,9 @@
     <t>建筑编号</t>
   </si>
   <si>
+    <t>受影响的雇员类型</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -136,6 +163,9 @@
   </si>
   <si>
     <t>UnlockCost</t>
+  </si>
+  <si>
+    <t>EmployeeProfile</t>
   </si>
   <si>
     <t>1990000_10000</t>
@@ -465,12 +495,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -806,7 +842,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -830,16 +866,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -848,89 +884,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -940,17 +976,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1483,7 +1522,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.875" customWidth="1"/>
@@ -1493,9 +1532,10 @@
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="8" max="8" width="18.25" customWidth="1"/>
     <col min="9" max="9" width="13.25" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,54 +1563,63 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9">
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1580,8 +1629,9 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <f>D5*1000+B5*100+C5</f>
         <v>1101</v>
@@ -1597,19 +1647,22 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>21</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A27" si="0">D6*1000+B6*100+C6</f>
         <v>1102</v>
@@ -1627,19 +1680,22 @@
         <v>1101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>23</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1103</v>
@@ -1657,19 +1713,22 @@
         <v>1102</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>1104</v>
@@ -1687,19 +1746,22 @@
         <v>1103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>27</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>1105</v>
@@ -1717,19 +1779,22 @@
         <v>1104</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>29</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>1106</v>
@@ -1747,19 +1812,22 @@
         <v>1105</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>31</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>1107</v>
@@ -1777,19 +1845,22 @@
         <v>1106</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>33</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>1108</v>
@@ -1807,19 +1878,22 @@
         <v>1107</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>35</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>1109</v>
@@ -1837,19 +1911,22 @@
         <v>1108</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>37</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
@@ -1867,19 +1944,22 @@
         <v>1109</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>39</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>1111</v>
@@ -1897,19 +1977,22 @@
         <v>1110</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>41</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J15" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>1112</v>
@@ -1927,19 +2010,22 @@
         <v>1111</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>43</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>1201</v>
@@ -1955,19 +2041,22 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>46</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>1202</v>
@@ -1985,19 +2074,22 @@
         <v>1201</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>48</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>1301</v>
@@ -2013,19 +2105,22 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>51</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>1302</v>
@@ -2041,19 +2136,22 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>53</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>1303</v>
@@ -2069,19 +2167,22 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>55</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J21" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>1304</v>
@@ -2097,19 +2198,22 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>57</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>1401</v>
@@ -2125,19 +2229,19 @@
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>1402</v>
@@ -2153,19 +2257,19 @@
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>59</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>1403</v>
@@ -2181,19 +2285,19 @@
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>59</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>1404</v>
@@ -2209,19 +2313,19 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>59</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>1405</v>
@@ -2237,16 +2341,16 @@
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>67</v>
+        <v>59</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
